--- a/jogos_2025-01-20.xlsx
+++ b/jogos_2025-01-20.xlsx
@@ -1030,19 +1030,19 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kheybar Khorramabad</t>
+          <t>Aluminium Arak</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Havadar</t>
+          <t>Esteghlal Khuzestan</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I5" t="n">
         <v>1</v>
@@ -1056,83 +1056,83 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M5" t="n">
-        <v>2.85</v>
+        <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.37</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['35', '87']</t>
+          <t>['12']</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['58']</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.48</v>
+        <v>1.78</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK5" s="3" t="n">
         <v>45677.35416666666</v>
@@ -1159,19 +1159,19 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Aluminium Arak</t>
+          <t>Kheybar Khorramabad</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Esteghlal Khuzestan</t>
+          <t>Havadar</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
         <v>1</v>
@@ -1185,83 +1185,83 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>2.15</v>
+        <v>2.4</v>
       </c>
       <c r="M6" t="n">
-        <v>2.5</v>
+        <v>2.85</v>
       </c>
       <c r="N6" t="n">
-        <v>4</v>
+        <v>3.15</v>
       </c>
       <c r="O6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>5.25</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>['12']</t>
+          <t>['35', '87']</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>['58']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG6" t="n">
-        <v>1.22</v>
+        <v>1.28</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.78</v>
+        <v>1.48</v>
       </c>
       <c r="AI6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
         <v>45677.35416666666</v>
@@ -1278,7 +1278,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>Iran Persian Gulf Pro League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>PSIS Semarang</t>
+          <t>Esteghlal</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>Shams Azar Qazvin</t>
         </is>
       </c>
       <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
         <v>1</v>
       </c>
-      <c r="H7" t="n">
-        <v>2</v>
-      </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>2.03</v>
+        <v>1.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N7" t="n">
-        <v>3.3</v>
+        <v>7.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.6</v>
+        <v>2.1</v>
       </c>
       <c r="P7" t="n">
-        <v>2.03</v>
+        <v>1.91</v>
       </c>
       <c r="Q7" t="n">
-        <v>4.1</v>
+        <v>8.5</v>
       </c>
       <c r="R7" t="n">
         <v>1.49</v>
       </c>
       <c r="S7" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="T7" t="n">
-        <v>2.9</v>
+        <v>3.2</v>
       </c>
       <c r="U7" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AD7" t="n">
         <v>1.33</v>
       </c>
-      <c r="X7" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>['76']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>['20', '32']</t>
+          <t>['64']</t>
         </is>
       </c>
       <c r="AG7" t="n">
-        <v>1.24</v>
+        <v>1.11</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.61</v>
+        <v>2.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>1.72</v>
+        <v>1.33</v>
       </c>
       <c r="AJ7" t="n">
-        <v>2.54</v>
+        <v>5.5</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45677.375</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Iran Persian Gulf Pro League</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,25 +1675,25 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esteghlal</t>
+          <t>PSIS Semarang</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Shams Azar Qazvin</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
@@ -1701,83 +1701,83 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>1.5</v>
+        <v>2.03</v>
       </c>
       <c r="M10" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N10" t="n">
         <v>3.3</v>
       </c>
-      <c r="N10" t="n">
-        <v>7.5</v>
-      </c>
       <c r="O10" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>2.03</v>
       </c>
       <c r="Q10" t="n">
-        <v>8.5</v>
+        <v>4.1</v>
       </c>
       <c r="R10" t="n">
         <v>1.49</v>
       </c>
       <c r="S10" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="T10" t="n">
-        <v>3.2</v>
+        <v>2.9</v>
       </c>
       <c r="U10" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="V10" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="X10" t="n">
-        <v>2.6</v>
+        <v>3.05</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.75</v>
+        <v>2.04</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="AA10" t="n">
-        <v>4.75</v>
+        <v>3.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>1.17</v>
+        <v>1.26</v>
       </c>
       <c r="AC10" t="n">
-        <v>3</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['76']</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>['64']</t>
+          <t>['20', '32']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>1.11</v>
+        <v>1.24</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.3</v>
+        <v>1.61</v>
       </c>
       <c r="AI10" t="n">
-        <v>1.33</v>
+        <v>1.72</v>
       </c>
       <c r="AJ10" t="n">
-        <v>5.5</v>
+        <v>2.54</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45677.375</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,25 +2320,25 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Hapoel Petah Tikva</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.6</v>
+        <v>4.63</v>
       </c>
       <c r="M15" t="n">
-        <v>3.6</v>
+        <v>3.88</v>
       </c>
       <c r="N15" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="O15" t="n">
         <v>4.75</v>
       </c>
-      <c r="O15" t="n">
-        <v>2.2</v>
-      </c>
       <c r="P15" t="n">
-        <v>2.1</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>5.5</v>
+        <v>2.15</v>
       </c>
       <c r="R15" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="S15" t="n">
         <v>3</v>
       </c>
       <c r="T15" t="n">
-        <v>2.75</v>
+        <v>2.55</v>
       </c>
       <c r="U15" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="V15" t="n">
         <v>1.04</v>
       </c>
       <c r="W15" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="X15" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="Y15" t="n">
-        <v>2.08</v>
+        <v>1.83</v>
       </c>
       <c r="Z15" t="n">
-        <v>1.73</v>
+        <v>1.96</v>
       </c>
       <c r="AA15" t="n">
         <v>3</v>
       </c>
       <c r="AB15" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.1</v>
+        <v>1.73</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.67</v>
+        <v>1.95</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['58', '63', '79']</t>
+          <t>['90+1']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['30', '63']</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.24</v>
+        <v>2.15</v>
       </c>
       <c r="AH15" t="n">
-        <v>1.8</v>
+        <v>1.18</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>2.8</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3.25</v>
+        <v>1.55</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45677.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,25 +2449,25 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hapoel Tel Aviv</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K16" t="inlineStr">
         <is>
@@ -2475,83 +2475,83 @@
         </is>
       </c>
       <c r="L16" t="n">
-        <v>6.25</v>
+        <v>1.48</v>
       </c>
       <c r="M16" t="n">
-        <v>4.33</v>
+        <v>4.49</v>
       </c>
       <c r="N16" t="n">
-        <v>1.4</v>
+        <v>6.06</v>
       </c>
       <c r="O16" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.91</v>
+        <v>5.5</v>
       </c>
       <c r="R16" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>3.75</v>
       </c>
       <c r="T16" t="n">
-        <v>2.75</v>
+        <v>2.4</v>
       </c>
       <c r="U16" t="n">
-        <v>1.4</v>
+        <v>1.62</v>
       </c>
       <c r="V16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W16" t="n">
-        <v>1.25</v>
+        <v>1.17</v>
       </c>
       <c r="X16" t="n">
-        <v>3.6</v>
+        <v>4.75</v>
       </c>
       <c r="Y16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC16" t="n">
         <v>1.7</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AD16" t="n">
         <v>2.1</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>['6', '13', '31', '86']</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG16" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AJ16" t="n">
         <v>2.85</v>
-      </c>
-      <c r="AB16" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="AC16" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AD16" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>['27']</t>
-        </is>
-      </c>
-      <c r="AG16" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AH16" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="AI16" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AJ16" t="n">
-        <v>1.25</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45677.58333333334</v>
@@ -2578,19 +2578,19 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Petah Tikva</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H17" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
@@ -2604,83 +2604,83 @@
         </is>
       </c>
       <c r="L17" t="n">
-        <v>2.8</v>
+        <v>1.6</v>
       </c>
       <c r="M17" t="n">
-        <v>3.9</v>
+        <v>3.6</v>
       </c>
       <c r="N17" t="n">
-        <v>2</v>
+        <v>4.75</v>
       </c>
       <c r="O17" t="n">
-        <v>3.5</v>
+        <v>2.2</v>
       </c>
       <c r="P17" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.6</v>
+        <v>5.5</v>
       </c>
       <c r="R17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S17" t="n">
+        <v>3</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W17" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X17" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB17" t="n">
         <v>1.33</v>
       </c>
-      <c r="S17" t="n">
+      <c r="AC17" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>['58', '63', '79']</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG17" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ17" t="n">
         <v>3.25</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="U17" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="W17" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X17" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>['52', '74']</t>
-        </is>
-      </c>
-      <c r="AG17" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AH17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>1.67</v>
       </c>
       <c r="AK17" s="3" t="n">
         <v>45677.58333333334</v>
@@ -2707,19 +2707,19 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Ironi Ramat HaSharon</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I18" t="n">
         <v>0</v>
@@ -2733,22 +2733,22 @@
         </is>
       </c>
       <c r="L18" t="n">
-        <v>3.4</v>
+        <v>2.8</v>
       </c>
       <c r="M18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N18" t="n">
+        <v>2</v>
+      </c>
+      <c r="O18" t="n">
         <v>3.5</v>
       </c>
-      <c r="N18" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="O18" t="n">
-        <v>4</v>
-      </c>
       <c r="P18" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="R18" t="n">
         <v>1.33</v>
@@ -2757,37 +2757,37 @@
         <v>3.25</v>
       </c>
       <c r="T18" t="n">
-        <v>2.5</v>
+        <v>2.63</v>
       </c>
       <c r="U18" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="V18" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="W18" t="n">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="X18" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="Z18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AA18" t="n">
-        <v>2.8</v>
+        <v>2.65</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="AC18" t="n">
-        <v>1.73</v>
+        <v>1.57</v>
       </c>
       <c r="AD18" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
@@ -2796,20 +2796,20 @@
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['52', '74']</t>
         </is>
       </c>
       <c r="AG18" t="n">
-        <v>1.34</v>
+        <v>1.41</v>
       </c>
       <c r="AH18" t="n">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="AI18" t="n">
-        <v>2.5</v>
+        <v>2.25</v>
       </c>
       <c r="AJ18" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="AK18" s="3" t="n">
         <v>45677.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,22 +2836,22 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Gençlerbirliği</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Kocaelispor</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H19" t="n">
         <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -2862,65 +2862,65 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>1.48</v>
+        <v>2.98</v>
       </c>
       <c r="M19" t="n">
-        <v>4.49</v>
+        <v>3.22</v>
       </c>
       <c r="N19" t="n">
-        <v>6.06</v>
+        <v>2.26</v>
       </c>
       <c r="O19" t="n">
-        <v>2</v>
+        <v>3.68</v>
       </c>
       <c r="P19" t="n">
-        <v>2.5</v>
+        <v>2.01</v>
       </c>
       <c r="Q19" t="n">
-        <v>5.5</v>
+        <v>2.88</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="S19" t="n">
-        <v>3.75</v>
+        <v>2.65</v>
       </c>
       <c r="T19" t="n">
-        <v>2.4</v>
+        <v>3.1</v>
       </c>
       <c r="U19" t="n">
-        <v>1.62</v>
+        <v>1.34</v>
       </c>
       <c r="V19" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="W19" t="n">
-        <v>1.17</v>
+        <v>1.33</v>
       </c>
       <c r="X19" t="n">
-        <v>4.75</v>
+        <v>2.83</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="Z19" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="AA19" t="n">
-        <v>2.45</v>
+        <v>3.58</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.52</v>
+        <v>1.21</v>
       </c>
       <c r="AC19" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="AD19" t="n">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['6', '13', '31', '86']</t>
+          <t>['45+3']</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -2929,16 +2929,16 @@
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.15</v>
+        <v>1.55</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.7</v>
+        <v>1.33</v>
       </c>
       <c r="AI19" t="n">
-        <v>1.42</v>
+        <v>2.22</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.85</v>
+        <v>1.87</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45677.58333333334</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,25 +2965,25 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Ironi Ramat HaSharon</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" t="inlineStr">
         <is>
@@ -2991,52 +2991,52 @@
         </is>
       </c>
       <c r="L20" t="n">
-        <v>4.63</v>
+        <v>3.4</v>
       </c>
       <c r="M20" t="n">
-        <v>3.88</v>
+        <v>3.5</v>
       </c>
       <c r="N20" t="n">
-        <v>1.67</v>
+        <v>1.83</v>
       </c>
       <c r="O20" t="n">
-        <v>4.75</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="R20" t="n">
         <v>1.33</v>
       </c>
       <c r="S20" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="T20" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="U20" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="V20" t="n">
         <v>1.04</v>
       </c>
       <c r="W20" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="X20" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="Z20" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AA20" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AB20" t="n">
         <v>1.38</v>
@@ -3045,29 +3045,29 @@
         <v>1.73</v>
       </c>
       <c r="AD20" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>['90+1']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['30', '63']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>2.15</v>
+        <v>1.34</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45677.58333333334</v>
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -3094,109 +3094,109 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Gençlerbirliği</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kocaelispor</t>
+          <t>Hapoel Tel Aviv</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
         <v>1</v>
       </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
       <c r="K21" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.98</v>
+        <v>6.25</v>
       </c>
       <c r="M21" t="n">
-        <v>3.22</v>
+        <v>4.33</v>
       </c>
       <c r="N21" t="n">
-        <v>2.26</v>
+        <v>1.4</v>
       </c>
       <c r="O21" t="n">
-        <v>3.68</v>
+        <v>6.5</v>
       </c>
       <c r="P21" t="n">
-        <v>2.01</v>
+        <v>2.38</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.88</v>
+        <v>1.91</v>
       </c>
       <c r="R21" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="S21" t="n">
-        <v>2.65</v>
+        <v>3</v>
       </c>
       <c r="T21" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="U21" t="n">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="V21" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="X21" t="n">
-        <v>2.83</v>
+        <v>3.6</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.08</v>
+        <v>1.7</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.67</v>
+        <v>2.1</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.58</v>
+        <v>2.85</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.21</v>
+        <v>1.37</v>
       </c>
       <c r="AC21" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="AD21" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>['45+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['27']</t>
         </is>
       </c>
       <c r="AG21" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH21" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="AI21" t="n">
-        <v>2.22</v>
+        <v>4.33</v>
       </c>
       <c r="AJ21" t="n">
-        <v>1.87</v>
+        <v>1.25</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45677.58333333334</v>
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,109 +3223,109 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FC Penafiel</t>
+          <t>CSM Iaşi</t>
         </is>
       </c>
       <c r="G22" t="n">
         <v>2</v>
       </c>
       <c r="H22" t="n">
+        <v>1</v>
+      </c>
+      <c r="I22" t="n">
         <v>2</v>
       </c>
-      <c r="I22" t="n">
+      <c r="J22" t="n">
         <v>1</v>
       </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
       <c r="K22" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L22" t="n">
-        <v>4</v>
+        <v>1.53</v>
       </c>
       <c r="M22" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="N22" t="n">
-        <v>1.95</v>
+        <v>5.8</v>
       </c>
       <c r="O22" t="n">
-        <v>4.2</v>
+        <v>2.14</v>
       </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="R22" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="S22" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="T22" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="U22" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="V22" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="W22" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="X22" t="n">
         <v>3.1</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.8</v>
+        <v>2.02</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.95</v>
+        <v>1.68</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>['13', '64']</t>
+          <t>['20', '40']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>['52', '84']</t>
+          <t>['35']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.75</v>
+        <v>1.12</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.25</v>
+        <v>2.11</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.64</v>
+        <v>1.47</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.66</v>
+        <v>3.2</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45677.625</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,109 +3481,109 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>CSM Iaşi</t>
+          <t>FC Penafiel</t>
         </is>
       </c>
       <c r="G24" t="n">
         <v>2</v>
       </c>
       <c r="H24" t="n">
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L24" t="n">
+        <v>4</v>
+      </c>
+      <c r="M24" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N24" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="O24" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="P24" t="n">
         <v>2</v>
       </c>
-      <c r="J24" t="n">
-        <v>1</v>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L24" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="M24" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="N24" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="O24" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="P24" t="n">
-        <v>2.15</v>
-      </c>
       <c r="Q24" t="n">
-        <v>6</v>
+        <v>2.7</v>
       </c>
       <c r="R24" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="S24" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="T24" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="U24" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="V24" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="X24" t="n">
         <v>3.1</v>
       </c>
       <c r="Y24" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="AA24" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="AC24" t="n">
-        <v>2.02</v>
+        <v>1.8</v>
       </c>
       <c r="AD24" t="n">
-        <v>1.68</v>
+        <v>1.95</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>['20', '40']</t>
+          <t>['13', '64']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['35']</t>
+          <t>['52', '84']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.12</v>
+        <v>1.75</v>
       </c>
       <c r="AH24" t="n">
-        <v>2.11</v>
+        <v>1.25</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.47</v>
+        <v>2.64</v>
       </c>
       <c r="AJ24" t="n">
-        <v>3.2</v>
+        <v>1.66</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45677.625</v>
@@ -3739,22 +3739,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>2.55</v>
+        <v>1.72</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>4.06</v>
       </c>
       <c r="N26" t="n">
-        <v>2.55</v>
+        <v>4.28</v>
       </c>
       <c r="O26" t="n">
-        <v>3.1</v>
+        <v>2.25</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.6</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.1</v>
+        <v>4</v>
       </c>
       <c r="R26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U26" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="X26" t="n">
+        <v>7</v>
+      </c>
+      <c r="Y26" t="n">
         <v>1.33</v>
       </c>
-      <c r="S26" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="T26" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="U26" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W26" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X26" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>1.67</v>
-      </c>
       <c r="Z26" t="n">
-        <v>2.15</v>
+        <v>3.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.47</v>
+        <v>1.94</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.53</v>
+        <v>1.36</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.38</v>
+        <v>3</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
+          <t>['17', '28', '55', '90+5']</t>
+        </is>
+      </c>
+      <c r="AF26" t="inlineStr">
+        <is>
           <t>[]</t>
         </is>
       </c>
-      <c r="AF26" t="inlineStr">
-        <is>
-          <t>['88']</t>
-        </is>
-      </c>
       <c r="AG26" t="n">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.8</v>
+        <v>1.6</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.05</v>
+        <v>2.4</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45677.66666666666</v>
@@ -3868,22 +3868,22 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="G27" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I27" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -3894,83 +3894,83 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>1.72</v>
+        <v>4.7</v>
       </c>
       <c r="M27" t="n">
-        <v>4.06</v>
+        <v>4.37</v>
       </c>
       <c r="N27" t="n">
-        <v>4.28</v>
+        <v>1.61</v>
       </c>
       <c r="O27" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P27" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="R27" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W27" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X27" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD27" t="n">
         <v>2.25</v>
       </c>
-      <c r="P27" t="n">
+      <c r="AE27" t="inlineStr">
+        <is>
+          <t>['41']</t>
+        </is>
+      </c>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>['86']</t>
+        </is>
+      </c>
+      <c r="AG27" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AI27" t="n">
         <v>2.6</v>
       </c>
-      <c r="Q27" t="n">
-        <v>4</v>
-      </c>
-      <c r="R27" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="S27" t="n">
-        <v>4.25</v>
-      </c>
-      <c r="T27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U27" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W27" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="X27" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE27" t="inlineStr">
-        <is>
-          <t>['17', '28', '55', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF27" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG27" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>1.6</v>
-      </c>
       <c r="AJ27" t="n">
-        <v>2.4</v>
+        <v>1.55</v>
       </c>
       <c r="AK27" s="3" t="n">
         <v>45677.66666666666</v>
@@ -3997,22 +3997,22 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="G28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
         <v>1</v>
       </c>
       <c r="I28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J28" t="n">
         <v>0</v>
@@ -4023,83 +4023,83 @@
         </is>
       </c>
       <c r="L28" t="n">
-        <v>4.7</v>
+        <v>2.55</v>
       </c>
       <c r="M28" t="n">
-        <v>4.37</v>
+        <v>3.5</v>
       </c>
       <c r="N28" t="n">
-        <v>1.61</v>
+        <v>2.55</v>
       </c>
       <c r="O28" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="P28" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R28" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="T28" t="n">
         <v>2.5</v>
       </c>
-      <c r="Q28" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="R28" t="n">
-        <v>1.26</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T28" t="n">
-        <v>2.34</v>
-      </c>
       <c r="U28" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="V28" t="n">
         <v>1.02</v>
       </c>
       <c r="W28" t="n">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="X28" t="n">
-        <v>4.75</v>
+        <v>4.33</v>
       </c>
       <c r="Y28" t="n">
-        <v>1.6</v>
+        <v>1.67</v>
       </c>
       <c r="Z28" t="n">
-        <v>2.3</v>
+        <v>2.15</v>
       </c>
       <c r="AA28" t="n">
-        <v>2.55</v>
+        <v>2.7</v>
       </c>
       <c r="AB28" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AE28" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF28" t="inlineStr">
+        <is>
+          <t>['88']</t>
+        </is>
+      </c>
+      <c r="AG28" t="n">
         <v>1.52</v>
       </c>
-      <c r="AC28" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="AE28" t="inlineStr">
-        <is>
-          <t>['41']</t>
-        </is>
-      </c>
-      <c r="AF28" t="inlineStr">
-        <is>
-          <t>['86']</t>
-        </is>
-      </c>
-      <c r="AG28" t="n">
-        <v>2.2</v>
-      </c>
       <c r="AH28" t="n">
-        <v>1.2</v>
+        <v>1.53</v>
       </c>
       <c r="AI28" t="n">
-        <v>2.6</v>
+        <v>1.8</v>
       </c>
       <c r="AJ28" t="n">
-        <v>1.55</v>
+        <v>2.05</v>
       </c>
       <c r="AK28" s="3" t="n">
         <v>45677.66666666666</v>
@@ -4245,7 +4245,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -4255,16 +4255,16 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Messina</t>
+          <t>Mirandés</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Crotone</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H30" t="n">
         <v>2</v>
@@ -4281,83 +4281,83 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>4.75</v>
+        <v>2.1</v>
       </c>
       <c r="M30" t="n">
-        <v>3.5</v>
+        <v>2.88</v>
       </c>
       <c r="N30" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="O30" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P30" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>5</v>
+      </c>
+      <c r="R30" t="n">
         <v>1.62</v>
       </c>
-      <c r="O30" t="n">
-        <v>5</v>
-      </c>
-      <c r="P30" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="T30" t="n">
+        <v>4</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="W30" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="X30" t="n">
         <v>2.25</v>
       </c>
-      <c r="R30" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="n">
+      <c r="Y30" t="n">
         <v>2.75</v>
       </c>
-      <c r="U30" t="n">
+      <c r="Z30" t="n">
         <v>1.4</v>
       </c>
-      <c r="V30" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="W30" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="X30" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y30" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Z30" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AA30" t="n">
-        <v>3.1</v>
+        <v>5.75</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.3</v>
+        <v>1.12</v>
       </c>
       <c r="AC30" t="n">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="AD30" t="n">
-        <v>1.73</v>
+        <v>1.53</v>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['57', '61', '90+3']</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
         <is>
-          <t>['40', '60']</t>
+          <t>['40', '71']</t>
         </is>
       </c>
       <c r="AG30" t="n">
-        <v>2.4</v>
+        <v>1.22</v>
       </c>
       <c r="AH30" t="n">
-        <v>1.08</v>
+        <v>1.72</v>
       </c>
       <c r="AI30" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="AJ30" t="n">
-        <v>1.44</v>
+        <v>2.88</v>
       </c>
       <c r="AK30" s="3" t="n">
         <v>45677.6875</v>
@@ -4374,7 +4374,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -4384,25 +4384,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Mirandés</t>
+          <t>Gubbio</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="G31" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H31" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
       </c>
       <c r="J31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K31" t="inlineStr">
         <is>
@@ -4410,83 +4410,83 @@
         </is>
       </c>
       <c r="L31" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="M31" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="N31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O31" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="P31" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="R31" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="S31" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="W31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X31" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC31" t="n">
         <v>2.1</v>
       </c>
-      <c r="M31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="N31" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="O31" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="P31" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="Q31" t="n">
-        <v>5</v>
-      </c>
-      <c r="R31" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="S31" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="T31" t="n">
-        <v>4</v>
-      </c>
-      <c r="U31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="V31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="W31" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="X31" t="n">
+      <c r="AD31" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AE31" t="inlineStr">
+        <is>
+          <t>['90+3']</t>
+        </is>
+      </c>
+      <c r="AF31" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG31" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AI31" t="n">
         <v>2.25</v>
       </c>
-      <c r="Y31" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="Z31" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AA31" t="n">
-        <v>5.75</v>
-      </c>
-      <c r="AB31" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="AC31" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AD31" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="AE31" t="inlineStr">
-        <is>
-          <t>['57', '61', '90+3']</t>
-        </is>
-      </c>
-      <c r="AF31" t="inlineStr">
-        <is>
-          <t>['40', '71']</t>
-        </is>
-      </c>
-      <c r="AG31" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH31" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AI31" t="n">
-        <v>1.67</v>
-      </c>
       <c r="AJ31" t="n">
-        <v>2.88</v>
+        <v>1.95</v>
       </c>
       <c r="AK31" s="3" t="n">
         <v>45677.6875</v>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,109 +4513,109 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Gubbio</t>
+          <t>Messina</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Crotone</t>
         </is>
       </c>
       <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>2</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
         <v>1</v>
       </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L32" t="n">
-        <v>2.88</v>
+        <v>4.75</v>
       </c>
       <c r="M32" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N32" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O32" t="n">
+        <v>5</v>
+      </c>
+      <c r="P32" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="R32" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="S32" t="n">
+        <v>3</v>
+      </c>
+      <c r="T32" t="n">
         <v>2.75</v>
       </c>
-      <c r="N32" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="O32" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="P32" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="Q32" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="R32" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="S32" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="T32" t="n">
+      <c r="U32" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W32" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="X32" t="n">
         <v>3.5</v>
       </c>
-      <c r="U32" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W32" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X32" t="n">
-        <v>2.65</v>
-      </c>
       <c r="Y32" t="n">
-        <v>2.5</v>
+        <v>1.95</v>
       </c>
       <c r="Z32" t="n">
-        <v>1.5</v>
+        <v>1.85</v>
       </c>
       <c r="AA32" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AB32" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="AC32" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AD32" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>['90+3']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['40', '60']</t>
         </is>
       </c>
       <c r="AG32" t="n">
-        <v>1.41</v>
+        <v>2.4</v>
       </c>
       <c r="AH32" t="n">
-        <v>1.4</v>
+        <v>1.08</v>
       </c>
       <c r="AI32" t="n">
-        <v>2.25</v>
+        <v>3.1</v>
       </c>
       <c r="AJ32" t="n">
-        <v>1.95</v>
+        <v>1.44</v>
       </c>
       <c r="AK32" s="3" t="n">
         <v>45677.6875</v>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,25 +4642,25 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Troyes</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Annecy</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H33" t="n">
         <v>1</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" t="inlineStr">
         <is>
@@ -4671,31 +4671,31 @@
         <v>2</v>
       </c>
       <c r="M33" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="N33" t="n">
         <v>3.6</v>
       </c>
       <c r="O33" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="P33" t="n">
         <v>2.1</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.33</v>
+        <v>4</v>
       </c>
       <c r="R33" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S33" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="T33" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="U33" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="V33" t="n">
         <v>1.06</v>
@@ -4704,16 +4704,16 @@
         <v>1.33</v>
       </c>
       <c r="X33" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="Y33" t="n">
-        <v>2.03</v>
+        <v>2</v>
       </c>
       <c r="Z33" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="AA33" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="AB33" t="n">
         <v>1.28</v>
@@ -4722,26 +4722,26 @@
         <v>1.8</v>
       </c>
       <c r="AD33" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="AE33" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['5', '44', '78', '90']</t>
         </is>
       </c>
       <c r="AF33" t="inlineStr">
         <is>
-          <t>['4']</t>
+          <t>['50']</t>
         </is>
       </c>
       <c r="AG33" t="n">
         <v>1.28</v>
       </c>
       <c r="AH33" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="AI33" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AJ33" t="n">
         <v>2.5</v>
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,25 +4771,25 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Troyes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Annecy</t>
         </is>
       </c>
       <c r="G34" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
         <v>1</v>
       </c>
       <c r="I34" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K34" t="inlineStr">
         <is>
@@ -4800,31 +4800,31 @@
         <v>2</v>
       </c>
       <c r="M34" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N34" t="n">
         <v>3.6</v>
       </c>
       <c r="O34" t="n">
-        <v>2.75</v>
+        <v>2.63</v>
       </c>
       <c r="P34" t="n">
         <v>2.1</v>
       </c>
       <c r="Q34" t="n">
-        <v>4</v>
+        <v>4.33</v>
       </c>
       <c r="R34" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="S34" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="T34" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="U34" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="V34" t="n">
         <v>1.06</v>
@@ -4833,16 +4833,16 @@
         <v>1.33</v>
       </c>
       <c r="X34" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="Y34" t="n">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="Z34" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AA34" t="n">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="AB34" t="n">
         <v>1.28</v>
@@ -4851,26 +4851,26 @@
         <v>1.8</v>
       </c>
       <c r="AD34" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="AE34" t="inlineStr">
         <is>
-          <t>['5', '44', '78', '90']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF34" t="inlineStr">
         <is>
-          <t>['50']</t>
+          <t>['4']</t>
         </is>
       </c>
       <c r="AG34" t="n">
         <v>1.28</v>
       </c>
       <c r="AH34" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="AI34" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AJ34" t="n">
         <v>2.5</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -4900,25 +4900,25 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>RCD Mallorca</t>
         </is>
       </c>
       <c r="G35" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I35" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="inlineStr">
         <is>
@@ -4926,83 +4926,83 @@
         </is>
       </c>
       <c r="L35" t="n">
-        <v>1.36</v>
+        <v>1.73</v>
       </c>
       <c r="M35" t="n">
-        <v>5.6</v>
+        <v>3.5</v>
       </c>
       <c r="N35" t="n">
-        <v>6.5</v>
+        <v>5.25</v>
       </c>
       <c r="O35" t="n">
-        <v>1.73</v>
+        <v>2.38</v>
       </c>
       <c r="P35" t="n">
-        <v>2.88</v>
+        <v>2.1</v>
       </c>
       <c r="Q35" t="n">
-        <v>6.5</v>
+        <v>5.5</v>
       </c>
       <c r="R35" t="n">
-        <v>1.2</v>
+        <v>1.44</v>
       </c>
       <c r="S35" t="n">
-        <v>4.33</v>
+        <v>2.63</v>
       </c>
       <c r="T35" t="n">
-        <v>1.91</v>
+        <v>3.25</v>
       </c>
       <c r="U35" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="X35" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>2</v>
+      </c>
+      <c r="Z35" t="n">
         <v>1.8</v>
       </c>
-      <c r="V35" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W35" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="X35" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="Z35" t="n">
+      <c r="AA35" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AE35" t="inlineStr">
+        <is>
+          <t>['20', '24', '26', '28']</t>
+        </is>
+      </c>
+      <c r="AF35" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG35" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AJ35" t="n">
         <v>3.1</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AE35" t="inlineStr">
-        <is>
-          <t>['24', '60', '65']</t>
-        </is>
-      </c>
-      <c r="AF35" t="inlineStr">
-        <is>
-          <t>['45+5']</t>
-        </is>
-      </c>
-      <c r="AG35" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>3.75</v>
       </c>
       <c r="AK35" s="3" t="n">
         <v>45677.70833333334</v>
@@ -5019,7 +5019,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -5029,25 +5029,25 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>RCD Mallorca</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="G36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I36" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K36" t="inlineStr">
         <is>
@@ -5055,83 +5055,83 @@
         </is>
       </c>
       <c r="L36" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="M36" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="N36" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="O36" t="n">
         <v>1.73</v>
       </c>
-      <c r="M36" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N36" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="O36" t="n">
-        <v>2.38</v>
-      </c>
       <c r="P36" t="n">
-        <v>2.1</v>
+        <v>2.88</v>
       </c>
       <c r="Q36" t="n">
-        <v>5.5</v>
+        <v>6.5</v>
       </c>
       <c r="R36" t="n">
-        <v>1.44</v>
+        <v>1.2</v>
       </c>
       <c r="S36" t="n">
-        <v>2.63</v>
+        <v>4.33</v>
       </c>
       <c r="T36" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="U36" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="V36" t="n">
-        <v>1.06</v>
+        <v>1.01</v>
       </c>
       <c r="W36" t="n">
-        <v>1.35</v>
+        <v>1.1</v>
       </c>
       <c r="X36" t="n">
-        <v>3.25</v>
+        <v>7.6</v>
       </c>
       <c r="Y36" t="n">
-        <v>2</v>
+        <v>1.36</v>
       </c>
       <c r="Z36" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="AA36" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AE36" t="inlineStr">
+        <is>
+          <t>['24', '60', '65']</t>
+        </is>
+      </c>
+      <c r="AF36" t="inlineStr">
+        <is>
+          <t>['45+5']</t>
+        </is>
+      </c>
+      <c r="AG36" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AJ36" t="n">
         <v>3.75</v>
-      </c>
-      <c r="AB36" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="AC36" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AD36" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AE36" t="inlineStr">
-        <is>
-          <t>['20', '24', '26', '28']</t>
-        </is>
-      </c>
-      <c r="AF36" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG36" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AH36" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI36" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AJ36" t="n">
-        <v>3.1</v>
       </c>
       <c r="AK36" s="3" t="n">
         <v>45677.70833333334</v>
